--- a/wiki/reports/daily/2026-09-22_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-22_일일보고.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="165" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,11 +74,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,7 +200,13 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +613,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-22 07:53   |   전일: 9월 21일   |   월평균 기준: 이전 작업일 15일 평균   |   9월 누적 작업일: 16일</t>
+          <t>생성: 2026-09-22 16:00   |   전일: 9월 21일   |   월평균 기준: 이전 작업일 15일 평균   |   9월 누적 작업일: 16일</t>
         </is>
       </c>
     </row>
@@ -674,25 +675,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>45</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-45</v>
+        <v>-27</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>30.3</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-30.26666666666667</v>
+        <v>-12.26666666666667</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-1</v>
+        <v>-0.4052863436123348</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -703,29 +704,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>2527</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>11547</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-11547</v>
+        <v>-9020</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-1</v>
+        <v>-0.7811552784272972</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7930.8</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-7930.8</v>
+        <v>-5403.8</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-1</v>
+        <v>-0.6813688404700661</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>0:00:00</t>
+          <t>0:42:07</t>
         </is>
       </c>
     </row>
@@ -736,25 +737,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>27</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-19</v>
+        <v>-14</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.7037037037037037</v>
+        <v>-0.5185185185185185</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>18.3</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-10.26666666666667</v>
+        <v>-5.266666666666666</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.5620437956204379</v>
+        <v>-0.2883211678832117</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -765,29 +766,29 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4720</v>
+        <v>5757</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>12606</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>-7886</v>
+        <v>-6849</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-0.6255751229573219</v>
+        <v>-0.5433127082341742</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>7050</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-2330</v>
+        <v>-1293</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.3304964539007092</v>
+        <v>-0.1834042553191489</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>1:18:40</t>
+          <t>1:35:57</t>
         </is>
       </c>
     </row>
@@ -798,25 +799,25 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>72</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-64</v>
+        <v>-41</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.8888888888888888</v>
+        <v>-0.5694444444444444</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>48.5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-40.53333333333333</v>
+        <v>-17.53333333333333</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.8351648351648352</v>
+        <v>-0.3612637362637363</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
@@ -827,29 +828,29 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>4720</v>
+        <v>8284</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>24153</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-19433</v>
+        <v>-15869</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.8045791413074981</v>
+        <v>-0.6570198319049394</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>14980.8</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-10260.8</v>
+        <v>-6696.799999999999</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.6849300437893837</v>
+        <v>-0.4470255260066218</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>1:18:40</t>
+          <t>2:18:04</t>
         </is>
       </c>
     </row>
@@ -860,25 +861,25 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>72</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-64</v>
+        <v>-41</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.8888888888888888</v>
+        <v>-0.5694444444444444</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>47.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-39.66666666666666</v>
+        <v>-16.66666666666666</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.8321678321678322</v>
+        <v>-0.3496503496503496</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
@@ -890,13 +891,13 @@
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="n">
-        <v>736</v>
+        <v>759</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>229432</v>
+        <v>232996</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>723</v>
+        <v>746</v>
       </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="13" t="n"/>
@@ -919,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1006,122 +1007,207 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>(해당일 작업 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>■ GX7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>순서</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>형상</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>날수(F)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>날경(Ø)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>상크경(Ø)</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>코팅</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>특이사항</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>수량(개)</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="inlineStr">
-        <is>
-          <t>시간합계(초)</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>시간(H:M:S)</t>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>0106</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>1820</v>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>0:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr"/>
+      <c r="I5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>176</v>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
+        <is>
+          <t>0:02:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>면취</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>526</v>
+      </c>
+      <c r="K6" s="17" t="inlineStr">
+        <is>
+          <t>0:08:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="17" t="inlineStr">
+        <is>
+          <t>0:00:04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>평_라핑</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>볼</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>뮤</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
-        <is>
-          <t>0202</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>4720</v>
-      </c>
-      <c r="K8" s="20" t="inlineStr">
-        <is>
-          <t>1:18:40</t>
+      <c r="J8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="17" t="inlineStr">
+        <is>
+          <t>0:00:01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>GX7 소계</t>
+          <t>FAST GRIND 소계</t>
         </is>
       </c>
       <c r="B9" s="13" t="n"/>
@@ -1132,23 +1218,231 @@
       <c r="G9" s="13" t="n"/>
       <c r="H9" s="13" t="n"/>
       <c r="I9" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>2527</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>0:42:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>■ GX7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>형상</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>날수(F)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>날경(Ø)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>상크경(Ø)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>코팅</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>특이사항</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>수량(개)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>시간합계(초)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>시간(H:M:S)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>0202</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr"/>
+      <c r="I13" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J13" s="24" t="n">
         <v>4720</v>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>1:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr"/>
+      <c r="I14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="24" t="n">
+        <v>1035</v>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>0:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>평_라핑</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
+      <c r="I15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
+        <is>
+          <t>0:00:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>GX7 소계</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>5757</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>1:35:57</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
